--- a/Cehua/Excel/关卡配置.xlsx
+++ b/Cehua/Excel/关卡配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGame\MiniGame\ArrowsGameGit\ArrowsGame\Cehua\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="关卡配置" sheetId="4" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="87">
   <si>
     <t>0 使用布局配置
 1使用种子和生成参数进行生成
@@ -67,6 +72,9 @@
     <t>是否显示彩色点</t>
   </si>
   <si>
+    <t>关卡时间</t>
+  </si>
+  <si>
     <t>MultiRowMap#1#-1#levelsCfg#@levelId#int</t>
   </si>
   <si>
@@ -110,6 +118,9 @@
   </si>
   <si>
     <t>isPointColorful</t>
+  </si>
+  <si>
+    <t>timeLimitSeconds</t>
   </si>
   <si>
     <t>-1</t>
@@ -1252,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="73.2222222222222" style="7" customWidth="1"/>
@@ -1266,12 +1277,12 @@
     <col min="11" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="96.6" spans="1:10">
+    <row r="1" ht="96.6" spans="1:11">
       <c r="C1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1302,215 +1313,236 @@
       <c r="J2" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="27.6" spans="1:10">
+    </row>
+    <row r="4" ht="27.6" spans="1:11">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>26</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K5" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="J6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="J7" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K7" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="7">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="7">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7">
-        <v>1</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="J8" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K8" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -1519,30 +1551,33 @@
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K9" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G10" s="7">
         <v>1</v>
@@ -1551,30 +1586,33 @@
         <v>1</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K10" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" s="7">
         <v>1</v>
@@ -1583,30 +1621,33 @@
         <v>1</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K11" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G12" s="7">
         <v>1</v>
@@ -1615,30 +1656,33 @@
         <v>1</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K12" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G13" s="7">
         <v>1</v>
@@ -1647,30 +1691,33 @@
         <v>1</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K13" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
         <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G14" s="7">
         <v>1</v>
@@ -1679,30 +1726,33 @@
         <v>1</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K14" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
         <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G15" s="7">
         <v>1</v>
@@ -1711,30 +1761,33 @@
         <v>1</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K15" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G16" s="7">
         <v>1</v>
@@ -1743,30 +1796,33 @@
         <v>1</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K16" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G17" s="7">
         <v>1</v>
@@ -1775,30 +1831,33 @@
         <v>1</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K17" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G18" s="7">
         <v>1</v>
@@ -1807,30 +1866,33 @@
         <v>1</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K18" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2">
         <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G19" s="7">
         <v>1</v>
@@ -1839,30 +1901,33 @@
         <v>1</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K19" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
         <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G20" s="7">
         <v>1</v>
@@ -1871,30 +1936,33 @@
         <v>1</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="K20" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2">
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G21" s="7">
         <v>1</v>
@@ -1903,13 +1971,16 @@
         <v>1</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>32</v>
+      </c>
+      <c r="K21" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
@@ -1917,7 +1988,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -1925,7 +1996,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
@@ -1933,7 +2004,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
@@ -1941,7 +2012,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
@@ -1949,7 +2020,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1957,7 +2028,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="3"/>
@@ -1965,7 +2036,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="3"/>
@@ -1973,7 +2044,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="3"/>
@@ -1981,7 +2052,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="3"/>
@@ -2279,37 +2350,37 @@
   <sheetData>
     <row r="2" ht="27.6" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="5"/>
@@ -2318,37 +2389,37 @@
     </row>
     <row r="3" ht="41.4" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="6"/>
@@ -2357,37 +2428,37 @@
     </row>
     <row r="4" ht="27.6" spans="1:15">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -2396,37 +2467,37 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -2435,7 +2506,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -2459,13 +2530,13 @@
         <v>10</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -2547,30 +2618,30 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="27.6" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2584,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2598,7 +2669,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
